--- a/LISTAS_ORDENADAS/MI/Tornillos Pitones Arandelas Tuercas/TANQUE.xlsx
+++ b/LISTAS_ORDENADAS/MI/Tornillos Pitones Arandelas Tuercas/TANQUE.xlsx
@@ -759,7 +759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col width="12.5703125" customWidth="1" style="13" min="1" max="1"/>
@@ -770,13 +770,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45201.68855027235</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
+        <v>45266</v>
+      </c>
+    </row>
     <row r="6" ht="22.5" customHeight="1" s="13">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -799,8 +795,6 @@
       </c>
       <c r="E8" s="16" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="13">
       <c r="A11" s="14" t="inlineStr">
         <is>
@@ -811,17 +805,6 @@
     <row r="12" ht="41.25" customHeight="1" s="13">
       <c r="A12" s="15" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
     <row r="24" ht="33.75" customHeight="1" s="13">
       <c r="B24" s="12" t="inlineStr">
         <is>
@@ -829,8 +812,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
     <row r="27" ht="18" customHeight="1" s="13">
       <c r="A27" s="4" t="inlineStr">
         <is>
@@ -1360,8 +1341,6 @@
         <v>5707.184</v>
       </c>
     </row>
-    <row r="63"/>
-    <row r="64"/>
     <row r="65" ht="33.75" customHeight="1" s="13">
       <c r="B65" s="12" t="inlineStr">
         <is>
@@ -1468,7 +1447,7 @@
       </c>
       <c r="C72" s="20" t="n"/>
       <c r="D72" s="11" t="n">
-        <v>953.141</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1" s="13">
@@ -1647,8 +1626,6 @@
         <v>3125.665</v>
       </c>
     </row>
-    <row r="84"/>
-    <row r="85"/>
     <row r="86" ht="33.75" customHeight="1" s="13">
       <c r="B86" s="12" t="inlineStr">
         <is>
@@ -1656,7 +1633,6 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
     <row r="88" ht="18" customHeight="1" s="13">
       <c r="A88" s="4" t="inlineStr">
         <is>
@@ -1867,8 +1843,6 @@
         <v>1068.042</v>
       </c>
     </row>
-    <row r="101"/>
-    <row r="102"/>
     <row r="103" ht="33.75" customHeight="1" s="13">
       <c r="B103" s="12" t="inlineStr">
         <is>
@@ -1876,7 +1850,6 @@
         </is>
       </c>
     </row>
-    <row r="104"/>
     <row r="105" ht="18" customHeight="1" s="13">
       <c r="A105" s="4" t="inlineStr">
         <is>
@@ -2119,87 +2092,86 @@
         <v>7782.528</v>
       </c>
     </row>
-    <row r="120"/>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B51:C51"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B92:C92"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B59:C59"/>
     <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B70:C70"/>
     <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B111:C111"/>
     <mergeCell ref="B73:C73"/>
     <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B110:C110"/>
     <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
